--- a/database/event/5285/event_5285_evp_summary.xlsx
+++ b/database/event/5285/event_5285_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.0504</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7829</v>
+        <v>2.7162</v>
       </c>
       <c r="E2" t="n">
         <v>7.9319</v>
@@ -548,7 +548,7 @@
         <v>3.9647</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7152</v>
+        <v>2.6493</v>
       </c>
       <c r="E3" t="n">
         <v>7.7641</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4256</v>
+        <v>6.3887</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2812</v>
+        <v>3.2624</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1744</v>
+        <v>2.1013</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4256</v>
+        <v>6.3887</v>
       </c>
       <c r="F4" t="n">
-        <v>6.4256</v>
+        <v>6.3887</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.7722</v>
+        <v>7.7143</v>
       </c>
       <c r="I4" t="n">
         <v>7.8447</v>
@@ -640,7 +640,7 @@
         <v>3.1829</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0966</v>
+        <v>2.0393</v>
       </c>
       <c r="E5" t="n">
         <v>6.233</v>
@@ -686,7 +686,7 @@
         <v>2.9659</v>
       </c>
       <c r="D6" t="n">
-        <v>1.925</v>
+        <v>1.87</v>
       </c>
       <c r="E6" t="n">
         <v>5.8081</v>
@@ -732,7 +732,7 @@
         <v>2.9053</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8771</v>
+        <v>1.8228</v>
       </c>
       <c r="E7" t="n">
         <v>5.6895</v>
@@ -778,7 +778,7 @@
         <v>2.4979</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5547</v>
+        <v>1.5049</v>
       </c>
       <c r="E8" t="n">
         <v>4.8916</v>
@@ -824,7 +824,7 @@
         <v>2.3535</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4405</v>
+        <v>1.3922</v>
       </c>
       <c r="E9" t="n">
         <v>4.6088</v>
@@ -870,7 +870,7 @@
         <v>2.2505</v>
       </c>
       <c r="D10" t="n">
-        <v>1.359</v>
+        <v>1.3119</v>
       </c>
       <c r="E10" t="n">
         <v>4.4071</v>
@@ -916,7 +916,7 @@
         <v>2.1978</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3173</v>
+        <v>1.2708</v>
       </c>
       <c r="E11" t="n">
         <v>4.3039</v>
@@ -962,7 +962,7 @@
         <v>2.1658</v>
       </c>
       <c r="D12" t="n">
-        <v>1.292</v>
+        <v>1.2458</v>
       </c>
       <c r="E12" t="n">
         <v>4.2412</v>
@@ -1008,7 +1008,7 @@
         <v>2.1223</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2576</v>
+        <v>1.2119</v>
       </c>
       <c r="E13" t="n">
         <v>4.1561</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.9983</v>
+        <v>3.9834</v>
       </c>
       <c r="C14" t="n">
-        <v>2.0417</v>
+        <v>2.0341</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1939</v>
+        <v>1.1431</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9983</v>
+        <v>3.9834</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9983</v>
+        <v>3.9834</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9983</v>
+        <v>3.9834</v>
       </c>
       <c r="I14" t="n">
         <v>4.0169</v>
@@ -1090,185 +1090,185 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9866</v>
+        <v>3.9783</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0358</v>
+        <v>2.0315</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1891</v>
+        <v>1.141</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9866</v>
+        <v>3.9783</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9866</v>
+        <v>3.9783</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9866</v>
+        <v>3.9783</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0238</v>
+        <v>3.9783</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.0238</v>
+        <v>3.9783</v>
       </c>
       <c r="N15" t="n">
-        <v>309</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.9783</v>
+        <v>3.9569</v>
       </c>
       <c r="C16" t="n">
-        <v>2.0315</v>
+        <v>2.0206</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1858</v>
+        <v>1.1325</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9783</v>
+        <v>3.9569</v>
       </c>
       <c r="F16" t="n">
-        <v>3.9783</v>
+        <v>3.9569</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9783</v>
+        <v>3.9569</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9783</v>
+        <v>4.0238</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>346</v>
+        <v>309</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9783</v>
+        <v>4.0238</v>
       </c>
       <c r="N16" t="n">
-        <v>346</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.7633</v>
+        <v>3.757</v>
       </c>
       <c r="C17" t="n">
-        <v>1.9217</v>
+        <v>1.9185</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0989</v>
+        <v>1.0529</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7633</v>
+        <v>3.757</v>
       </c>
       <c r="F17" t="n">
-        <v>3.7633</v>
+        <v>4.0643</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.3073</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7633</v>
+        <v>4.0643</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7808</v>
+        <v>3.2942</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.3073</v>
       </c>
       <c r="K17" t="n">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7808</v>
+        <v>2.9869</v>
       </c>
       <c r="N17" t="n">
-        <v>397</v>
+        <v>472</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.757</v>
+        <v>3.7493</v>
       </c>
       <c r="C18" t="n">
-        <v>1.9185</v>
+        <v>1.9146</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0964</v>
+        <v>1.0498</v>
       </c>
       <c r="E18" t="n">
-        <v>3.757</v>
+        <v>3.7493</v>
       </c>
       <c r="F18" t="n">
-        <v>4.0643</v>
+        <v>3.7493</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3073</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4.0643</v>
+        <v>3.7493</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2942</v>
+        <v>3.7808</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3073</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>426</v>
+        <v>397</v>
       </c>
       <c r="L18" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9869</v>
+        <v>3.7808</v>
       </c>
       <c r="N18" t="n">
-        <v>472</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19">
@@ -1284,7 +1284,7 @@
         <v>1.7932</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9973</v>
+        <v>0.9552</v>
       </c>
       <c r="E19" t="n">
         <v>3.5117</v>
@@ -1330,7 +1330,7 @@
         <v>1.5456</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8014</v>
+        <v>0.7619</v>
       </c>
       <c r="E20" t="n">
         <v>3.0267</v>
@@ -1366,139 +1366,139 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.9817</v>
+        <v>2.9811</v>
       </c>
       <c r="C21" t="n">
-        <v>1.5226</v>
+        <v>1.5223</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7832</v>
+        <v>0.7438</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9817</v>
+        <v>2.9811</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9817</v>
+        <v>2.9811</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9817</v>
+        <v>2.9811</v>
       </c>
       <c r="I21" t="n">
-        <v>3.0095</v>
+        <v>2.9811</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.0095</v>
+        <v>2.9811</v>
       </c>
       <c r="N21" t="n">
-        <v>309</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.9811</v>
+        <v>2.9743</v>
       </c>
       <c r="C22" t="n">
-        <v>1.5223</v>
+        <v>1.5188</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7829</v>
+        <v>0.7411</v>
       </c>
       <c r="E22" t="n">
-        <v>2.9811</v>
+        <v>2.9743</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9811</v>
+        <v>3.145</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.1707</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9811</v>
+        <v>3.145</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9811</v>
+        <v>2.5491</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.1707</v>
       </c>
       <c r="K22" t="n">
-        <v>272</v>
+        <v>426</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9811</v>
+        <v>2.3784</v>
       </c>
       <c r="N22" t="n">
-        <v>272</v>
+        <v>472</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.9743</v>
+        <v>2.9595</v>
       </c>
       <c r="C23" t="n">
-        <v>1.5188</v>
+        <v>1.5113</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7802</v>
+        <v>0.7352</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9743</v>
+        <v>2.9595</v>
       </c>
       <c r="F23" t="n">
-        <v>3.145</v>
+        <v>2.9595</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1707</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.145</v>
+        <v>2.9595</v>
       </c>
       <c r="I23" t="n">
-        <v>2.5491</v>
+        <v>3.0095</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1707</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>426</v>
+        <v>309</v>
       </c>
       <c r="L23" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.3784</v>
+        <v>3.0095</v>
       </c>
       <c r="N23" t="n">
-        <v>472</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24">
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.9447</v>
+        <v>2.9337</v>
       </c>
       <c r="C24" t="n">
-        <v>1.5037</v>
+        <v>1.4981</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7682</v>
+        <v>0.7249</v>
       </c>
       <c r="E24" t="n">
-        <v>2.9447</v>
+        <v>2.9337</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9447</v>
+        <v>2.9337</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.9447</v>
+        <v>2.9337</v>
       </c>
       <c r="I24" t="n">
         <v>2.9584</v>
@@ -1560,7 +1560,7 @@
         <v>1.4868</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7549</v>
+        <v>0.7161</v>
       </c>
       <c r="E25" t="n">
         <v>2.9116</v>
@@ -1606,7 +1606,7 @@
         <v>1.4266</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.6691</v>
       </c>
       <c r="E26" t="n">
         <v>2.7936</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.6854</v>
+        <v>2.6754</v>
       </c>
       <c r="C27" t="n">
-        <v>1.3713</v>
+        <v>1.3662</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6635</v>
+        <v>0.622</v>
       </c>
       <c r="E27" t="n">
-        <v>2.6854</v>
+        <v>2.6754</v>
       </c>
       <c r="F27" t="n">
-        <v>2.6854</v>
+        <v>2.6754</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.6854</v>
+        <v>2.6754</v>
       </c>
       <c r="I27" t="n">
         <v>2.6979</v>
@@ -1698,7 +1698,7 @@
         <v>1.1968</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5254</v>
+        <v>0.4898</v>
       </c>
       <c r="E28" t="n">
         <v>2.3436</v>
@@ -1744,7 +1744,7 @@
         <v>1.1566</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4936</v>
+        <v>0.4585</v>
       </c>
       <c r="E29" t="n">
         <v>2.265</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.2618</v>
+        <v>2.2533</v>
       </c>
       <c r="C30" t="n">
-        <v>1.155</v>
+        <v>1.1506</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4924</v>
+        <v>0.4538</v>
       </c>
       <c r="E30" t="n">
-        <v>2.2618</v>
+        <v>2.2533</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2618</v>
+        <v>2.2533</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2618</v>
+        <v>2.2533</v>
       </c>
       <c r="I30" t="n">
         <v>2.2723</v>
@@ -1836,7 +1836,7 @@
         <v>1.0469</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4068</v>
+        <v>0.3728</v>
       </c>
       <c r="E31" t="n">
         <v>2.0501</v>
@@ -1882,7 +1882,7 @@
         <v>0.9147</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3022</v>
+        <v>0.2697</v>
       </c>
       <c r="E32" t="n">
         <v>1.7912</v>
@@ -1928,7 +1928,7 @@
         <v>0.9092</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2979</v>
+        <v>0.2654</v>
       </c>
       <c r="E33" t="n">
         <v>1.7805</v>
@@ -1974,7 +1974,7 @@
         <v>0.9001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2907</v>
+        <v>0.2583</v>
       </c>
       <c r="E34" t="n">
         <v>1.7627</v>
@@ -2020,7 +2020,7 @@
         <v>0.8501</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2511</v>
+        <v>0.2193</v>
       </c>
       <c r="E35" t="n">
         <v>1.6647</v>
@@ -2066,7 +2066,7 @@
         <v>0.7927999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2058</v>
+        <v>0.1746</v>
       </c>
       <c r="E36" t="n">
         <v>1.5525</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.4083</v>
+        <v>1.3978</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7191</v>
+        <v>0.7138</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1476</v>
+        <v>0.113</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4083</v>
+        <v>1.3978</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4083</v>
+        <v>1.3978</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4083</v>
+        <v>1.3978</v>
       </c>
       <c r="I37" t="n">
         <v>1.4214</v>
@@ -2158,7 +2158,7 @@
         <v>0.5538999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0168</v>
+        <v>-0.0118</v>
       </c>
       <c r="E38" t="n">
         <v>1.0846</v>
@@ -2204,7 +2204,7 @@
         <v>0.5406</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0063</v>
+        <v>-0.0221</v>
       </c>
       <c r="E39" t="n">
         <v>1.0587</v>
@@ -2250,7 +2250,7 @@
         <v>0.5392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0052</v>
+        <v>-0.0232</v>
       </c>
       <c r="E40" t="n">
         <v>1.056</v>
@@ -2296,7 +2296,7 @@
         <v>0.5209</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0375</v>
       </c>
       <c r="E41" t="n">
         <v>1.0201</v>
@@ -2342,7 +2342,7 @@
         <v>0.4749</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0457</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="E42" t="n">
         <v>0.9298999999999999</v>
@@ -2388,7 +2388,7 @@
         <v>0.4604</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0572</v>
+        <v>-0.0848</v>
       </c>
       <c r="E43" t="n">
         <v>0.9015</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7683</v>
+        <v>0.7654</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3923</v>
+        <v>0.3909</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.111</v>
+        <v>-0.139</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7683</v>
+        <v>0.7654</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7683</v>
+        <v>0.7654</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7683</v>
+        <v>0.7654</v>
       </c>
       <c r="I44" t="n">
         <v>0.7719</v>
@@ -2480,7 +2480,7 @@
         <v>0.2953</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1878</v>
+        <v>-0.2136</v>
       </c>
       <c r="E45" t="n">
         <v>0.5782</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5152</v>
+        <v>0.5114</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2631</v>
+        <v>0.2611</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2132</v>
+        <v>-0.2402</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5152</v>
+        <v>0.5114</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5152</v>
+        <v>0.5114</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5152</v>
+        <v>0.5114</v>
       </c>
       <c r="I46" t="n">
         <v>0.52</v>
@@ -2572,7 +2572,7 @@
         <v>0.2565</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2184</v>
+        <v>-0.2438</v>
       </c>
       <c r="E47" t="n">
         <v>0.5023</v>
@@ -2618,7 +2618,7 @@
         <v>0.2148</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2514</v>
+        <v>-0.2763</v>
       </c>
       <c r="E48" t="n">
         <v>0.4206</v>
@@ -2664,7 +2664,7 @@
         <v>0.1505</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3023</v>
+        <v>-0.3265</v>
       </c>
       <c r="E49" t="n">
         <v>0.2948</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.2389</v>
+        <v>0.238</v>
       </c>
       <c r="C50" t="n">
-        <v>0.122</v>
+        <v>0.1215</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3249</v>
+        <v>-0.3491</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2389</v>
+        <v>0.238</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2389</v>
+        <v>0.238</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2389</v>
+        <v>0.238</v>
       </c>
       <c r="I50" t="n">
         <v>0.24</v>
@@ -2756,7 +2756,7 @@
         <v>0.0489</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3827</v>
+        <v>-0.4057</v>
       </c>
       <c r="E51" t="n">
         <v>0.0958</v>
@@ -2802,7 +2802,7 @@
         <v>0.0362</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3927</v>
+        <v>-0.4157</v>
       </c>
       <c r="E52" t="n">
         <v>0.0709</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.037</v>
+        <v>0.0368</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0189</v>
+        <v>0.0188</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4064</v>
+        <v>-0.4292</v>
       </c>
       <c r="E53" t="n">
-        <v>0.037</v>
+        <v>0.0368</v>
       </c>
       <c r="F53" t="n">
-        <v>0.037</v>
+        <v>0.0368</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.037</v>
+        <v>0.0368</v>
       </c>
       <c r="I53" t="n">
         <v>0.0372</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0104</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4296</v>
+        <v>-0.452</v>
       </c>
       <c r="E54" t="n">
         <v>-0.0203</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0283</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4437</v>
+        <v>-0.466</v>
       </c>
       <c r="E55" t="n">
         <v>-0.0554</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0388</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4521</v>
+        <v>-0.4742</v>
       </c>
       <c r="E56" t="n">
         <v>-0.076</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1203</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5165</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2356</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1437</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.535</v>
+        <v>-0.556</v>
       </c>
       <c r="E58" t="n">
         <v>-0.2814</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1508</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5407</v>
+        <v>-0.5616</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2954</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2225</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5974</v>
+        <v>-0.6175</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4357</v>
@@ -3216,7 +3216,7 @@
         <v>-0.2289</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6024</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="E61" t="n">
         <v>-0.4482</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2885</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6496</v>
+        <v>-0.669</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5649999999999999</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2969</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6562</v>
+        <v>-0.6755</v>
       </c>
       <c r="E63" t="n">
         <v>-0.5814</v>
@@ -3354,7 +3354,7 @@
         <v>-0.359</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7054</v>
+        <v>-0.724</v>
       </c>
       <c r="E64" t="n">
         <v>-0.703</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7478</v>
+        <v>-0.745</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3819</v>
+        <v>-0.3804</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7235</v>
+        <v>-0.7407</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7478</v>
+        <v>-0.745</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.7478</v>
+        <v>-0.745</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.7478</v>
+        <v>-0.745</v>
       </c>
       <c r="I65" t="n">
         <v>-0.7513</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3851</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.726</v>
+        <v>-0.7444</v>
       </c>
       <c r="E66" t="n">
         <v>-0.7542</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4554</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7817</v>
+        <v>-0.7992</v>
       </c>
       <c r="E67" t="n">
         <v>-0.8919</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4665</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7904</v>
+        <v>-0.8079</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9136</v>
@@ -3584,7 +3584,7 @@
         <v>-0.4951</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8131</v>
+        <v>-0.8302</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9696</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5184</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8315</v>
+        <v>-0.8484</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0152</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7462</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0117</v>
+        <v>-1.0261</v>
       </c>
       <c r="E71" t="n">
         <v>-1.4613</v>
@@ -3722,7 +3722,7 @@
         <v>-0.8366</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0832</v>
+        <v>-1.0966</v>
       </c>
       <c r="E72" t="n">
         <v>-1.6384</v>
@@ -3768,7 +3768,7 @@
         <v>-1.0286</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2351</v>
+        <v>-1.2464</v>
       </c>
       <c r="E73" t="n">
         <v>-2.0142</v>
@@ -3814,7 +3814,7 @@
         <v>-1.0383</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2428</v>
+        <v>-1.254</v>
       </c>
       <c r="E74" t="n">
         <v>-2.0333</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-2.064</v>
+        <v>-2.0563</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.054</v>
+        <v>-1.05</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2552</v>
+        <v>-1.2631</v>
       </c>
       <c r="E75" t="n">
-        <v>-2.064</v>
+        <v>-2.0563</v>
       </c>
       <c r="F75" t="n">
-        <v>-2.064</v>
+        <v>-2.0563</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-2.064</v>
+        <v>-2.0563</v>
       </c>
       <c r="I75" t="n">
         <v>-2.0736</v>
@@ -3906,7 +3906,7 @@
         <v>-1.1815</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3561</v>
+        <v>-1.3657</v>
       </c>
       <c r="E76" t="n">
         <v>-2.3138</v>
@@ -3952,7 +3952,7 @@
         <v>-1.2324</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3963</v>
+        <v>-1.4054</v>
       </c>
       <c r="E77" t="n">
         <v>-2.4134</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.4292</v>
+        <v>-2.4201</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.2405</v>
+        <v>-1.2358</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4027</v>
+        <v>-1.4081</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.4292</v>
+        <v>-2.4201</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.4292</v>
+        <v>-2.4201</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.4292</v>
+        <v>-2.4201</v>
       </c>
       <c r="I78" t="n">
         <v>-2.4405</v>
@@ -4044,7 +4044,7 @@
         <v>-1.2924</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4437</v>
+        <v>-1.4522</v>
       </c>
       <c r="E79" t="n">
         <v>-2.5308</v>
@@ -4090,7 +4090,7 @@
         <v>-1.4878</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5984</v>
+        <v>-1.6047</v>
       </c>
       <c r="E80" t="n">
         <v>-2.9136</v>
@@ -4136,7 +4136,7 @@
         <v>-1.498</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.6064</v>
+        <v>-1.6126</v>
       </c>
       <c r="E81" t="n">
         <v>-2.9335</v>
@@ -4182,7 +4182,7 @@
         <v>-1.5015</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.6092</v>
+        <v>-1.6154</v>
       </c>
       <c r="E82" t="n">
         <v>-2.9404</v>
@@ -4228,7 +4228,7 @@
         <v>-1.8213</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.8622</v>
+        <v>-1.8649</v>
       </c>
       <c r="E83" t="n">
         <v>-3.5667</v>
@@ -4274,7 +4274,7 @@
         <v>-1.8674</v>
       </c>
       <c r="D84" t="n">
-        <v>-1.8987</v>
+        <v>-1.9009</v>
       </c>
       <c r="E84" t="n">
         <v>-3.657</v>
